--- a/midterm score_data.xlsx
+++ b/midterm score_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t713\Desktop\python\Check Midterm Grades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t713\Desktop\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A56B70F-2ACE-488C-8D74-58C0CB4A84D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BC3F2E-3235-4D47-B2F5-F61E5F55AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="校排" sheetId="1" r:id="rId1"/>
@@ -779,36 +779,6 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>67</v>
-      </c>
-      <c r="E2" s="2">
-        <v>57</v>
-      </c>
-      <c r="F2" s="2">
-        <v>62</v>
-      </c>
-      <c r="G2" s="2">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2">
-        <v>94</v>
-      </c>
-      <c r="I2" s="2">
-        <v>43</v>
-      </c>
-      <c r="J2" s="2">
-        <v>97</v>
-      </c>
-      <c r="K2" s="2">
-        <v>70</v>
-      </c>
-      <c r="L2" s="2">
-        <v>70</v>
-      </c>
-      <c r="M2" s="2">
-        <v>94</v>
-      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -820,36 +790,6 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
-        <v>70</v>
-      </c>
-      <c r="E3" s="2">
-        <v>91</v>
-      </c>
-      <c r="F3" s="2">
-        <v>97</v>
-      </c>
-      <c r="G3" s="2">
-        <v>84</v>
-      </c>
-      <c r="H3" s="2">
-        <v>68</v>
-      </c>
-      <c r="I3" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" s="2">
-        <v>89</v>
-      </c>
-      <c r="K3" s="2">
-        <v>87</v>
-      </c>
-      <c r="L3" s="2">
-        <v>90</v>
-      </c>
-      <c r="M3" s="2">
-        <v>94</v>
-      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -860,36 +800,6 @@
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2">
-        <v>85</v>
-      </c>
-      <c r="E4" s="2">
-        <v>48</v>
-      </c>
-      <c r="F4" s="2">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2">
-        <v>75</v>
-      </c>
-      <c r="H4" s="2">
-        <v>83</v>
-      </c>
-      <c r="I4" s="2">
-        <v>59</v>
-      </c>
-      <c r="J4" s="2">
-        <v>77</v>
-      </c>
-      <c r="K4" s="2">
-        <v>56</v>
-      </c>
-      <c r="L4" s="2">
-        <v>58</v>
-      </c>
-      <c r="M4" s="2">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -975,36 +885,6 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>71</v>
-      </c>
-      <c r="E2" s="2">
-        <v>78</v>
-      </c>
-      <c r="F2" s="2">
-        <v>43</v>
-      </c>
-      <c r="G2" s="2">
-        <v>73</v>
-      </c>
-      <c r="H2" s="2">
-        <v>52</v>
-      </c>
-      <c r="I2" s="2">
-        <v>71</v>
-      </c>
-      <c r="J2" s="2">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2">
-        <v>52</v>
-      </c>
-      <c r="L2" s="2">
-        <v>97</v>
-      </c>
-      <c r="M2" s="2">
-        <v>98</v>
-      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1016,36 +896,6 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
-        <v>62</v>
-      </c>
-      <c r="E3" s="2">
-        <v>53</v>
-      </c>
-      <c r="F3" s="2">
-        <v>92</v>
-      </c>
-      <c r="G3" s="2">
-        <v>76</v>
-      </c>
-      <c r="H3" s="2">
-        <v>96</v>
-      </c>
-      <c r="I3" s="2">
-        <v>54</v>
-      </c>
-      <c r="J3" s="2">
-        <v>73</v>
-      </c>
-      <c r="K3" s="2">
-        <v>75</v>
-      </c>
-      <c r="L3" s="2">
-        <v>92</v>
-      </c>
-      <c r="M3" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1056,36 +906,6 @@
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2">
-        <v>58</v>
-      </c>
-      <c r="E4" s="2">
-        <v>48</v>
-      </c>
-      <c r="F4" s="2">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2">
-        <v>57</v>
-      </c>
-      <c r="I4" s="2">
-        <v>90</v>
-      </c>
-      <c r="J4" s="2">
-        <v>68</v>
-      </c>
-      <c r="K4" s="2">
-        <v>62</v>
-      </c>
-      <c r="L4" s="2">
-        <v>77</v>
-      </c>
-      <c r="M4" s="2">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1171,36 +991,6 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>83</v>
-      </c>
-      <c r="E2" s="2">
-        <v>74</v>
-      </c>
-      <c r="F2" s="2">
-        <v>98</v>
-      </c>
-      <c r="G2" s="2">
-        <v>42</v>
-      </c>
-      <c r="H2" s="2">
-        <v>95</v>
-      </c>
-      <c r="I2" s="2">
-        <v>89</v>
-      </c>
-      <c r="J2" s="2">
-        <v>82</v>
-      </c>
-      <c r="K2" s="2">
-        <v>86</v>
-      </c>
-      <c r="L2" s="2">
-        <v>60</v>
-      </c>
-      <c r="M2" s="2">
-        <v>66</v>
-      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1212,36 +1002,6 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
-        <v>95</v>
-      </c>
-      <c r="E3" s="2">
-        <v>58</v>
-      </c>
-      <c r="F3" s="2">
-        <v>51</v>
-      </c>
-      <c r="G3" s="2">
-        <v>95</v>
-      </c>
-      <c r="H3" s="2">
-        <v>61</v>
-      </c>
-      <c r="I3" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" s="2">
-        <v>93</v>
-      </c>
-      <c r="K3" s="2">
-        <v>87</v>
-      </c>
-      <c r="L3" s="2">
-        <v>73</v>
-      </c>
-      <c r="M3" s="2">
-        <v>65</v>
-      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1252,36 +1012,6 @@
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2">
-        <v>56</v>
-      </c>
-      <c r="E4" s="2">
-        <v>76</v>
-      </c>
-      <c r="F4" s="2">
-        <v>61</v>
-      </c>
-      <c r="G4" s="2">
-        <v>63</v>
-      </c>
-      <c r="H4" s="2">
-        <v>54</v>
-      </c>
-      <c r="I4" s="2">
-        <v>58</v>
-      </c>
-      <c r="J4" s="2">
-        <v>51</v>
-      </c>
-      <c r="K4" s="2">
-        <v>75</v>
-      </c>
-      <c r="L4" s="2">
-        <v>46</v>
-      </c>
-      <c r="M4" s="2">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1367,36 +1097,6 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>62</v>
-      </c>
-      <c r="E2" s="2">
-        <v>48</v>
-      </c>
-      <c r="F2" s="2">
-        <v>63</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45</v>
-      </c>
-      <c r="H2" s="2">
-        <v>44</v>
-      </c>
-      <c r="I2" s="2">
-        <v>51</v>
-      </c>
-      <c r="J2" s="2">
-        <v>66</v>
-      </c>
-      <c r="K2" s="2">
-        <v>87</v>
-      </c>
-      <c r="L2" s="2">
-        <v>70</v>
-      </c>
-      <c r="M2" s="2">
-        <v>58</v>
-      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1408,36 +1108,6 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
-        <v>93</v>
-      </c>
-      <c r="E3" s="2">
-        <v>49</v>
-      </c>
-      <c r="F3" s="2">
-        <v>85</v>
-      </c>
-      <c r="G3" s="2">
-        <v>91</v>
-      </c>
-      <c r="H3" s="2">
-        <v>61</v>
-      </c>
-      <c r="I3" s="2">
-        <v>67</v>
-      </c>
-      <c r="J3" s="2">
-        <v>48</v>
-      </c>
-      <c r="K3" s="2">
-        <v>88</v>
-      </c>
-      <c r="L3" s="2">
-        <v>93</v>
-      </c>
-      <c r="M3" s="2">
-        <v>61</v>
-      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1448,36 +1118,6 @@
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2">
-        <v>71</v>
-      </c>
-      <c r="E4" s="2">
-        <v>50</v>
-      </c>
-      <c r="F4" s="2">
-        <v>48</v>
-      </c>
-      <c r="G4" s="2">
-        <v>51</v>
-      </c>
-      <c r="H4" s="2">
-        <v>61</v>
-      </c>
-      <c r="I4" s="2">
-        <v>51</v>
-      </c>
-      <c r="J4" s="2">
-        <v>45</v>
-      </c>
-      <c r="K4" s="2">
-        <v>43</v>
-      </c>
-      <c r="L4" s="2">
-        <v>46</v>
-      </c>
-      <c r="M4" s="2">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1563,36 +1203,16 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>91</v>
-      </c>
-      <c r="E2" s="2">
-        <v>75</v>
-      </c>
-      <c r="F2" s="2">
-        <v>40</v>
-      </c>
-      <c r="G2" s="2">
-        <v>49</v>
-      </c>
-      <c r="H2" s="2">
-        <v>49</v>
-      </c>
-      <c r="I2" s="2">
-        <v>87</v>
-      </c>
-      <c r="J2" s="2">
-        <v>88</v>
-      </c>
-      <c r="K2" s="2">
-        <v>75</v>
-      </c>
-      <c r="L2" s="2">
-        <v>74</v>
-      </c>
-      <c r="M2" s="2">
-        <v>45</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1604,36 +1224,16 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
-        <v>98</v>
-      </c>
-      <c r="E3" s="2">
-        <v>48</v>
-      </c>
-      <c r="F3" s="2">
-        <v>95</v>
-      </c>
-      <c r="G3" s="2">
-        <v>98</v>
-      </c>
-      <c r="H3" s="2">
-        <v>73</v>
-      </c>
-      <c r="I3" s="2">
-        <v>59</v>
-      </c>
-      <c r="J3" s="2">
-        <v>77</v>
-      </c>
-      <c r="K3" s="2">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2">
-        <v>75</v>
-      </c>
-      <c r="M3" s="2">
-        <v>98</v>
-      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1645,36 +1245,16 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
-        <v>93</v>
-      </c>
-      <c r="E4" s="2">
-        <v>85</v>
-      </c>
-      <c r="F4" s="2">
-        <v>48</v>
-      </c>
-      <c r="G4" s="2">
-        <v>44</v>
-      </c>
-      <c r="H4" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" s="2">
-        <v>69</v>
-      </c>
-      <c r="J4" s="2">
-        <v>83</v>
-      </c>
-      <c r="K4" s="2">
-        <v>69</v>
-      </c>
-      <c r="L4" s="2">
-        <v>85</v>
-      </c>
-      <c r="M4" s="2">
-        <v>98</v>
-      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>

--- a/midterm score_data.xlsx
+++ b/midterm score_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t713\Desktop\python\Check Midterm Grades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A56B70F-2ACE-488C-8D74-58C0CB4A84D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B3CF09-9E81-46B5-98CC-FB0C14643197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="8170" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="校排" sheetId="1" r:id="rId1"/>
@@ -613,6 +613,9 @@
       <c r="M2" s="2">
         <v>62</v>
       </c>
+      <c r="N2" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -654,6 +657,9 @@
       <c r="M3" s="2">
         <v>103</v>
       </c>
+      <c r="N3" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -694,6 +700,9 @@
       </c>
       <c r="M4" s="2">
         <v>281</v>
+      </c>
+      <c r="N4" s="2">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -809,6 +818,9 @@
       <c r="M2" s="2">
         <v>94</v>
       </c>
+      <c r="N2" s="2">
+        <v>95</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -850,6 +862,9 @@
       <c r="M3" s="2">
         <v>94</v>
       </c>
+      <c r="N3" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -890,6 +905,9 @@
       </c>
       <c r="M4" s="2">
         <v>92</v>
+      </c>
+      <c r="N4" s="2">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1005,6 +1023,9 @@
       <c r="M2" s="2">
         <v>98</v>
       </c>
+      <c r="N2" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1046,6 +1067,9 @@
       <c r="M3" s="2">
         <v>84</v>
       </c>
+      <c r="N3" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1086,6 +1110,9 @@
       </c>
       <c r="M4" s="2">
         <v>43</v>
+      </c>
+      <c r="N4" s="2">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1201,6 +1228,9 @@
       <c r="M2" s="2">
         <v>66</v>
       </c>
+      <c r="N2" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1242,6 +1272,9 @@
       <c r="M3" s="2">
         <v>65</v>
       </c>
+      <c r="N3" s="2">
+        <v>75</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1282,6 +1315,9 @@
       </c>
       <c r="M4" s="2">
         <v>98</v>
+      </c>
+      <c r="N4" s="2">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1397,6 +1433,9 @@
       <c r="M2" s="2">
         <v>58</v>
       </c>
+      <c r="N2" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1438,6 +1477,9 @@
       <c r="M3" s="2">
         <v>61</v>
       </c>
+      <c r="N3" s="2">
+        <v>81</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1478,6 +1520,9 @@
       </c>
       <c r="M4" s="2">
         <v>61</v>
+      </c>
+      <c r="N4" s="2">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1593,6 +1638,9 @@
       <c r="M2" s="2">
         <v>45</v>
       </c>
+      <c r="N2" s="3">
+        <v>88</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -1634,6 +1682,9 @@
       <c r="M3" s="2">
         <v>98</v>
       </c>
+      <c r="N3" s="3">
+        <v>89</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -1674,6 +1725,9 @@
       </c>
       <c r="M4" s="2">
         <v>98</v>
+      </c>
+      <c r="N4" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
